--- a/docs/example_output/table2.xlsx
+++ b/docs/example_output/table2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -780,6 +780,60 @@
   </si>
   <si>
     <t xml:space="preserve">Age, Mean±SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very high (N=175)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age, mean±sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American indian or alaska native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black or african american</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethnicity, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hispanic or latino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not hispanic or latino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical stage, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior treatment, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tissue sample type, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary tumor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solid tissue normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancer type, n (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colon adenocarcinoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rectum adenocarcinoma</t>
   </si>
 </sst>
 </file>

--- a/docs/example_output/table2.xlsx
+++ b/docs/example_output/table2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -834,6 +834,18 @@
   </si>
   <si>
     <t xml:space="preserve">Rectum adenocarcinoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Indian Or Alaska Native</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Or African American</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hispanic Or Latino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Hispanic Or Latino</t>
   </si>
 </sst>
 </file>
